--- a/VerveStacks_NGA_grids_kan/source_data/VerveStacks_NGA.xlsx
+++ b/VerveStacks_NGA_grids_kan/source_data/VerveStacks_NGA.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19CE9081-8325-40A5-B3DF-67CACD604232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB90D96E-B45F-448E-99F8-4D9F38BB0D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="27" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="26" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="25" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="24" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="23" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="32" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="31" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="30" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="29" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="28" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="9" r:id="rId6"/>
     <sheet name="historical_data" sheetId="8" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4426" uniqueCount="877">
   <si>
     <t>Time Slices</t>
   </si>
@@ -2497,6 +2497,204 @@
   </si>
   <si>
     <t xml:space="preserve">Stated Policies </t>
+  </si>
+  <si>
+    <t>e_w39469643-330</t>
+  </si>
+  <si>
+    <t>w39469643-330</t>
+  </si>
+  <si>
+    <t>e_w395182311-330</t>
+  </si>
+  <si>
+    <t>w395182311-330</t>
+  </si>
+  <si>
+    <t>e_w559542338-330</t>
+  </si>
+  <si>
+    <t>w559542338-330</t>
+  </si>
+  <si>
+    <t>e_w564430566-330</t>
+  </si>
+  <si>
+    <t>w564430566-330</t>
+  </si>
+  <si>
+    <t>e_w574152484-330</t>
+  </si>
+  <si>
+    <t>w574152484-330</t>
+  </si>
+  <si>
+    <t>e_w215459565-330</t>
+  </si>
+  <si>
+    <t>w215459565-330</t>
+  </si>
+  <si>
+    <t>e_w669957212-330</t>
+  </si>
+  <si>
+    <t>w669957212-330</t>
+  </si>
+  <si>
+    <t>e_NG21-330</t>
+  </si>
+  <si>
+    <t>NG21-330</t>
+  </si>
+  <si>
+    <t>e_w546666333-330</t>
+  </si>
+  <si>
+    <t>w546666333-330</t>
+  </si>
+  <si>
+    <t>e_NG15-330</t>
+  </si>
+  <si>
+    <t>NG15-330</t>
+  </si>
+  <si>
+    <t>e_NG18-330</t>
+  </si>
+  <si>
+    <t>NG18-330</t>
+  </si>
+  <si>
+    <t>e_NG17-330</t>
+  </si>
+  <si>
+    <t>NG17-330</t>
+  </si>
+  <si>
+    <t>e_w706082453-330</t>
+  </si>
+  <si>
+    <t>w706082453-330</t>
+  </si>
+  <si>
+    <t>e_w564429999-330</t>
+  </si>
+  <si>
+    <t>w564429999-330</t>
+  </si>
+  <si>
+    <t>e_w575706869-330</t>
+  </si>
+  <si>
+    <t>w575706869-330</t>
+  </si>
+  <si>
+    <t>e_w565866986-330</t>
+  </si>
+  <si>
+    <t>w565866986-330</t>
+  </si>
+  <si>
+    <t>e_w267122040-330</t>
+  </si>
+  <si>
+    <t>w267122040-330</t>
+  </si>
+  <si>
+    <t>e_w563715917-330</t>
+  </si>
+  <si>
+    <t>w563715917-330</t>
+  </si>
+  <si>
+    <t>e_w564445207-330</t>
+  </si>
+  <si>
+    <t>w564445207-330</t>
+  </si>
+  <si>
+    <t>e_w1057700475-330</t>
+  </si>
+  <si>
+    <t>w1057700475-330</t>
+  </si>
+  <si>
+    <t>e_w565081403-330</t>
+  </si>
+  <si>
+    <t>w565081403-330</t>
+  </si>
+  <si>
+    <t>e_w565847437-330</t>
+  </si>
+  <si>
+    <t>w565847437-330</t>
+  </si>
+  <si>
+    <t>e_NG7-330</t>
+  </si>
+  <si>
+    <t>NG7-330</t>
+  </si>
+  <si>
+    <t>e_w836122563-330</t>
+  </si>
+  <si>
+    <t>w836122563-330</t>
+  </si>
+  <si>
+    <t>e_w565486405-330</t>
+  </si>
+  <si>
+    <t>w565486405-330</t>
+  </si>
+  <si>
+    <t>e_w563732518-330</t>
+  </si>
+  <si>
+    <t>w563732518-330</t>
+  </si>
+  <si>
+    <t>e_w655273140-330</t>
+  </si>
+  <si>
+    <t>w655273140-330</t>
+  </si>
+  <si>
+    <t>e_w746582404-330</t>
+  </si>
+  <si>
+    <t>w746582404-330</t>
+  </si>
+  <si>
+    <t>e_w540463591-330</t>
+  </si>
+  <si>
+    <t>w540463591-330</t>
+  </si>
+  <si>
+    <t>e_w695826179-330</t>
+  </si>
+  <si>
+    <t>w695826179-330</t>
+  </si>
+  <si>
+    <t>e_w556550171-330</t>
+  </si>
+  <si>
+    <t>w556550171-330</t>
+  </si>
+  <si>
+    <t>e_NG3-330</t>
+  </si>
+  <si>
+    <t>NG3-330</t>
+  </si>
+  <si>
+    <t>e_w266617120-330</t>
+  </si>
+  <si>
+    <t>w266617120-330</t>
   </si>
 </sst>
 </file>
@@ -2620,7 +2818,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E7E2831-9F0F-A3BB-0843-E14D5DCC58CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B19D240-C7E8-D933-AF92-808DFE9FC623}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2675,7 +2873,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21540945-CDFB-0765-BD70-87F36D5A603E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8B9C95A-9DA8-AAF8-448D-1CDDE98123D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3026,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8990571C-061B-4E35-9050-9948A132D724}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441581E1-4099-466A-AA80-7FF10D172D23}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6154,7 +6352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E18596-2D07-4C8B-A61B-C187359E703D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9704369-0AAD-40A8-BAC5-26DA5C69AD12}">
   <dimension ref="B2:L9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6414,7 +6612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862FCE1D-742C-4268-970E-27A0E8981C62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D02AC9-95C8-4844-8A2D-A1067AACC1C9}">
   <dimension ref="B2:J104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9387,7 +9585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033ABD1-394E-4526-BFDB-6CB21014A300}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77932D2E-1552-489F-AC40-C8E47E4BC1FD}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9815,7 +10013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43ED9F1B-399C-47FC-970F-F293363C484E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA064FA2-B2F3-4DD5-9D5F-677A200A70CE}">
   <dimension ref="A1:Y233"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9954,7 +10152,10 @@
         <v>112</v>
       </c>
       <c r="J7" t="s">
-        <v>376</v>
+        <v>811</v>
+      </c>
+      <c r="K7" t="s">
+        <v>812</v>
       </c>
       <c r="L7">
         <v>0.9</v>
@@ -9998,7 +10199,10 @@
         <v>112</v>
       </c>
       <c r="J8" t="s">
-        <v>376</v>
+        <v>813</v>
+      </c>
+      <c r="K8" t="s">
+        <v>814</v>
       </c>
       <c r="L8">
         <v>0.45</v>
@@ -10042,7 +10246,10 @@
         <v>112</v>
       </c>
       <c r="J9" t="s">
-        <v>376</v>
+        <v>813</v>
+      </c>
+      <c r="K9" t="s">
+        <v>814</v>
       </c>
       <c r="L9">
         <v>0.45</v>
@@ -10086,7 +10293,10 @@
         <v>112</v>
       </c>
       <c r="J10" t="s">
-        <v>376</v>
+        <v>813</v>
+      </c>
+      <c r="K10" t="s">
+        <v>814</v>
       </c>
       <c r="L10">
         <v>0.45</v>
@@ -10130,7 +10340,10 @@
         <v>112</v>
       </c>
       <c r="J11" t="s">
-        <v>376</v>
+        <v>815</v>
+      </c>
+      <c r="K11" t="s">
+        <v>816</v>
       </c>
       <c r="L11">
         <v>0.5</v>
@@ -10174,7 +10387,10 @@
         <v>112</v>
       </c>
       <c r="J12" t="s">
-        <v>376</v>
+        <v>815</v>
+      </c>
+      <c r="K12" t="s">
+        <v>816</v>
       </c>
       <c r="L12">
         <v>0.5</v>
@@ -10218,7 +10434,10 @@
         <v>112</v>
       </c>
       <c r="J13" t="s">
-        <v>376</v>
+        <v>815</v>
+      </c>
+      <c r="K13" t="s">
+        <v>816</v>
       </c>
       <c r="L13">
         <v>0.5</v>
@@ -10262,7 +10481,10 @@
         <v>112</v>
       </c>
       <c r="J14" t="s">
-        <v>376</v>
+        <v>817</v>
+      </c>
+      <c r="K14" t="s">
+        <v>818</v>
       </c>
       <c r="L14">
         <v>0.54</v>
@@ -10306,7 +10528,10 @@
         <v>112</v>
       </c>
       <c r="J15" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K15" t="s">
+        <v>820</v>
       </c>
       <c r="L15">
         <v>0.5</v>
@@ -10350,7 +10575,10 @@
         <v>112</v>
       </c>
       <c r="J16" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K16" t="s">
+        <v>820</v>
       </c>
       <c r="L16">
         <v>0.5</v>
@@ -10394,7 +10622,10 @@
         <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K17" t="s">
+        <v>822</v>
       </c>
       <c r="L17">
         <v>0.28499999999999998</v>
@@ -10438,7 +10669,10 @@
         <v>112</v>
       </c>
       <c r="J18" t="s">
-        <v>376</v>
+        <v>823</v>
+      </c>
+      <c r="K18" t="s">
+        <v>824</v>
       </c>
       <c r="L18">
         <v>1.8</v>
@@ -10482,7 +10716,10 @@
         <v>112</v>
       </c>
       <c r="J19" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K19" t="s">
+        <v>826</v>
       </c>
       <c r="L19">
         <v>0.5</v>
@@ -10526,7 +10763,10 @@
         <v>112</v>
       </c>
       <c r="J20" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K20" t="s">
+        <v>828</v>
       </c>
       <c r="L20">
         <v>0.1</v>
@@ -10570,7 +10810,10 @@
         <v>112</v>
       </c>
       <c r="J21" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K21" t="s">
+        <v>828</v>
       </c>
       <c r="L21">
         <v>0.1</v>
@@ -10614,7 +10857,10 @@
         <v>112</v>
       </c>
       <c r="J22" t="s">
-        <v>376</v>
+        <v>829</v>
+      </c>
+      <c r="K22" t="s">
+        <v>830</v>
       </c>
       <c r="L22">
         <v>0.495</v>
@@ -10658,7 +10904,10 @@
         <v>112</v>
       </c>
       <c r="J23" t="s">
-        <v>376</v>
+        <v>831</v>
+      </c>
+      <c r="K23" t="s">
+        <v>832</v>
       </c>
       <c r="L23">
         <v>0.16500000000000001</v>
@@ -10702,7 +10951,10 @@
         <v>112</v>
       </c>
       <c r="J24" t="s">
-        <v>376</v>
+        <v>831</v>
+      </c>
+      <c r="K24" t="s">
+        <v>832</v>
       </c>
       <c r="L24">
         <v>0.16500000000000001</v>
@@ -10746,7 +10998,10 @@
         <v>112</v>
       </c>
       <c r="J25" t="s">
-        <v>376</v>
+        <v>831</v>
+      </c>
+      <c r="K25" t="s">
+        <v>832</v>
       </c>
       <c r="L25">
         <v>0.16500000000000001</v>
@@ -10790,7 +11045,10 @@
         <v>112</v>
       </c>
       <c r="J26" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K26" t="s">
+        <v>834</v>
       </c>
       <c r="L26">
         <v>0.125</v>
@@ -10834,7 +11092,10 @@
         <v>112</v>
       </c>
       <c r="J27" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K27" t="s">
+        <v>834</v>
       </c>
       <c r="L27">
         <v>0.125</v>
@@ -10878,7 +11139,10 @@
         <v>112</v>
       </c>
       <c r="J28" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K28" t="s">
+        <v>826</v>
       </c>
       <c r="L28">
         <v>0.13</v>
@@ -10922,7 +11186,10 @@
         <v>112</v>
       </c>
       <c r="J29" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K29" t="s">
+        <v>826</v>
       </c>
       <c r="L29">
         <v>0.13</v>
@@ -10966,7 +11233,10 @@
         <v>112</v>
       </c>
       <c r="J30" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K30" t="s">
+        <v>826</v>
       </c>
       <c r="L30">
         <v>0.1</v>
@@ -11010,7 +11280,10 @@
         <v>112</v>
       </c>
       <c r="J31" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K31" t="s">
+        <v>836</v>
       </c>
       <c r="L31">
         <v>0.15</v>
@@ -11054,7 +11327,10 @@
         <v>112</v>
       </c>
       <c r="J32" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K32" t="s">
+        <v>836</v>
       </c>
       <c r="L32">
         <v>0.15</v>
@@ -11098,7 +11374,10 @@
         <v>112</v>
       </c>
       <c r="J33" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K33" t="s">
+        <v>836</v>
       </c>
       <c r="L33">
         <v>0.15</v>
@@ -11142,7 +11421,10 @@
         <v>112</v>
       </c>
       <c r="J34" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K34" t="s">
+        <v>838</v>
       </c>
       <c r="L34">
         <v>0.14099999999999999</v>
@@ -11186,7 +11468,10 @@
         <v>112</v>
       </c>
       <c r="J35" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K35" t="s">
+        <v>838</v>
       </c>
       <c r="L35">
         <v>0.14099999999999999</v>
@@ -11230,7 +11515,10 @@
         <v>112</v>
       </c>
       <c r="J36" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K36" t="s">
+        <v>838</v>
       </c>
       <c r="L36">
         <v>0.14099999999999999</v>
@@ -11274,7 +11562,10 @@
         <v>112</v>
       </c>
       <c r="J37" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K37" t="s">
+        <v>838</v>
       </c>
       <c r="L37">
         <v>0.14099999999999999</v>
@@ -11318,7 +11609,10 @@
         <v>112</v>
       </c>
       <c r="J38" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K38" t="s">
+        <v>834</v>
       </c>
       <c r="L38">
         <v>0.14849999999999999</v>
@@ -11362,7 +11656,10 @@
         <v>112</v>
       </c>
       <c r="J39" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K39" t="s">
+        <v>834</v>
       </c>
       <c r="L39">
         <v>0.14849999999999999</v>
@@ -11406,7 +11703,10 @@
         <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K40" t="s">
+        <v>834</v>
       </c>
       <c r="L40">
         <v>0.14849999999999999</v>
@@ -11450,7 +11750,10 @@
         <v>112</v>
       </c>
       <c r="J41" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K41" t="s">
+        <v>834</v>
       </c>
       <c r="L41">
         <v>0.14849999999999999</v>
@@ -11494,7 +11797,10 @@
         <v>112</v>
       </c>
       <c r="J42" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K42" t="s">
+        <v>822</v>
       </c>
       <c r="L42">
         <v>0.13800000000000001</v>
@@ -11538,7 +11844,10 @@
         <v>112</v>
       </c>
       <c r="J43" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K43" t="s">
+        <v>822</v>
       </c>
       <c r="L43">
         <v>0.13800000000000001</v>
@@ -11582,7 +11891,10 @@
         <v>112</v>
       </c>
       <c r="J44" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K44" t="s">
+        <v>822</v>
       </c>
       <c r="L44">
         <v>0.13800000000000001</v>
@@ -11626,7 +11938,10 @@
         <v>112</v>
       </c>
       <c r="J45" t="s">
-        <v>376</v>
+        <v>813</v>
+      </c>
+      <c r="K45" t="s">
+        <v>814</v>
       </c>
       <c r="L45">
         <v>0.15</v>
@@ -11670,7 +11985,10 @@
         <v>112</v>
       </c>
       <c r="J46" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K46" t="s">
+        <v>822</v>
       </c>
       <c r="L46">
         <v>0.434</v>
@@ -11714,7 +12032,10 @@
         <v>112</v>
       </c>
       <c r="J47" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K47" t="s">
+        <v>826</v>
       </c>
       <c r="L47">
         <v>0.125</v>
@@ -11758,7 +12079,10 @@
         <v>112</v>
       </c>
       <c r="J48" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K48" t="s">
+        <v>826</v>
       </c>
       <c r="L48">
         <v>0.125</v>
@@ -11802,7 +12126,10 @@
         <v>112</v>
       </c>
       <c r="J49" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K49" t="s">
+        <v>836</v>
       </c>
       <c r="L49">
         <v>0.11</v>
@@ -11846,7 +12173,10 @@
         <v>112</v>
       </c>
       <c r="J50" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K50" t="s">
+        <v>836</v>
       </c>
       <c r="L50">
         <v>0.11</v>
@@ -11890,7 +12220,10 @@
         <v>112</v>
       </c>
       <c r="J51" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K51" t="s">
+        <v>822</v>
       </c>
       <c r="L51">
         <v>0.16700000000000001</v>
@@ -11934,7 +12267,10 @@
         <v>112</v>
       </c>
       <c r="J52" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K52" t="s">
+        <v>822</v>
       </c>
       <c r="L52">
         <v>0.16700000000000001</v>
@@ -11978,7 +12314,10 @@
         <v>112</v>
       </c>
       <c r="J53" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K53" t="s">
+        <v>822</v>
       </c>
       <c r="L53">
         <v>0.16700000000000001</v>
@@ -12022,7 +12361,10 @@
         <v>112</v>
       </c>
       <c r="J54" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K54" t="s">
+        <v>836</v>
       </c>
       <c r="L54">
         <v>0.15</v>
@@ -12066,7 +12408,10 @@
         <v>112</v>
       </c>
       <c r="J55" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K55" t="s">
+        <v>836</v>
       </c>
       <c r="L55">
         <v>0.15</v>
@@ -12107,7 +12452,10 @@
         <v>112</v>
       </c>
       <c r="J56" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K56" t="s">
+        <v>836</v>
       </c>
       <c r="L56">
         <v>0.1</v>
@@ -12148,7 +12496,10 @@
         <v>112</v>
       </c>
       <c r="J57" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K57" t="s">
+        <v>836</v>
       </c>
       <c r="L57">
         <v>0.1</v>
@@ -12189,7 +12540,10 @@
         <v>112</v>
       </c>
       <c r="J58" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K58" t="s">
+        <v>836</v>
       </c>
       <c r="L58">
         <v>0.1</v>
@@ -12230,7 +12584,10 @@
         <v>112</v>
       </c>
       <c r="J59" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K59" t="s">
+        <v>836</v>
       </c>
       <c r="L59">
         <v>0.1</v>
@@ -12271,7 +12628,10 @@
         <v>112</v>
       </c>
       <c r="J60" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K60" t="s">
+        <v>836</v>
       </c>
       <c r="L60">
         <v>0.1</v>
@@ -12312,7 +12672,10 @@
         <v>112</v>
       </c>
       <c r="J61" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K61" t="s">
+        <v>836</v>
       </c>
       <c r="L61">
         <v>0.1</v>
@@ -12353,7 +12716,10 @@
         <v>112</v>
       </c>
       <c r="J62" t="s">
-        <v>376</v>
+        <v>835</v>
+      </c>
+      <c r="K62" t="s">
+        <v>836</v>
       </c>
       <c r="L62">
         <v>0.1</v>
@@ -12397,7 +12763,10 @@
         <v>112</v>
       </c>
       <c r="J63" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K63" t="s">
+        <v>828</v>
       </c>
       <c r="L63">
         <v>0.1</v>
@@ -12441,7 +12810,10 @@
         <v>112</v>
       </c>
       <c r="J64" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K64" t="s">
+        <v>828</v>
       </c>
       <c r="L64">
         <v>0.1</v>
@@ -12485,7 +12857,10 @@
         <v>112</v>
       </c>
       <c r="J65" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K65" t="s">
+        <v>828</v>
       </c>
       <c r="L65">
         <v>0.1</v>
@@ -12529,7 +12904,10 @@
         <v>112</v>
       </c>
       <c r="J66" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K66" t="s">
+        <v>828</v>
       </c>
       <c r="L66">
         <v>0.151</v>
@@ -12573,7 +12951,10 @@
         <v>112</v>
       </c>
       <c r="J67" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K67" t="s">
+        <v>828</v>
       </c>
       <c r="L67">
         <v>0.151</v>
@@ -12617,7 +12998,10 @@
         <v>112</v>
       </c>
       <c r="J68" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K68" t="s">
+        <v>828</v>
       </c>
       <c r="L68">
         <v>0.151</v>
@@ -12661,7 +13045,10 @@
         <v>112</v>
       </c>
       <c r="J69" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K69" t="s">
+        <v>822</v>
       </c>
       <c r="L69">
         <v>0.1</v>
@@ -12705,7 +13092,10 @@
         <v>112</v>
       </c>
       <c r="J70" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K70" t="s">
+        <v>822</v>
       </c>
       <c r="L70">
         <v>0.1</v>
@@ -12749,7 +13139,10 @@
         <v>112</v>
       </c>
       <c r="J71" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K71" t="s">
+        <v>822</v>
       </c>
       <c r="L71">
         <v>0.1</v>
@@ -12793,7 +13186,10 @@
         <v>112</v>
       </c>
       <c r="J72" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K72" t="s">
+        <v>822</v>
       </c>
       <c r="L72">
         <v>0.1</v>
@@ -12837,7 +13233,10 @@
         <v>112</v>
       </c>
       <c r="J73" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K73" t="s">
+        <v>822</v>
       </c>
       <c r="L73">
         <v>0.1</v>
@@ -12881,7 +13280,10 @@
         <v>112</v>
       </c>
       <c r="J74" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K74" t="s">
+        <v>822</v>
       </c>
       <c r="L74">
         <v>0.18</v>
@@ -12925,7 +13327,10 @@
         <v>112</v>
       </c>
       <c r="J75" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K75" t="s">
+        <v>822</v>
       </c>
       <c r="L75">
         <v>0.18</v>
@@ -12969,7 +13374,10 @@
         <v>112</v>
       </c>
       <c r="J76" t="s">
-        <v>376</v>
+        <v>831</v>
+      </c>
+      <c r="K76" t="s">
+        <v>832</v>
       </c>
       <c r="L76">
         <v>7.4999999999999997E-2</v>
@@ -13013,7 +13421,10 @@
         <v>112</v>
       </c>
       <c r="J77" t="s">
-        <v>376</v>
+        <v>831</v>
+      </c>
+      <c r="K77" t="s">
+        <v>832</v>
       </c>
       <c r="L77">
         <v>7.4999999999999997E-2</v>
@@ -13057,7 +13468,10 @@
         <v>112</v>
       </c>
       <c r="J78" t="s">
-        <v>376</v>
+        <v>831</v>
+      </c>
+      <c r="K78" t="s">
+        <v>832</v>
       </c>
       <c r="L78">
         <v>7.4999999999999997E-2</v>
@@ -13101,7 +13515,10 @@
         <v>112</v>
       </c>
       <c r="J79" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K79" t="s">
+        <v>834</v>
       </c>
       <c r="L79">
         <v>0.125</v>
@@ -13145,7 +13562,10 @@
         <v>112</v>
       </c>
       <c r="J80" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K80" t="s">
+        <v>838</v>
       </c>
       <c r="L80">
         <v>0.127</v>
@@ -13189,7 +13609,10 @@
         <v>112</v>
       </c>
       <c r="J81" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K81" t="s">
+        <v>838</v>
       </c>
       <c r="L81">
         <v>0.127</v>
@@ -13233,7 +13656,10 @@
         <v>112</v>
       </c>
       <c r="J82" t="s">
-        <v>376</v>
+        <v>839</v>
+      </c>
+      <c r="K82" t="s">
+        <v>840</v>
       </c>
       <c r="L82">
         <v>0.127</v>
@@ -13277,7 +13703,10 @@
         <v>112</v>
       </c>
       <c r="J83" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K83" t="s">
+        <v>834</v>
       </c>
       <c r="L83">
         <v>0.115</v>
@@ -13321,7 +13750,10 @@
         <v>112</v>
       </c>
       <c r="J84" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K84" t="s">
+        <v>820</v>
       </c>
       <c r="L84">
         <v>0.127</v>
@@ -13365,7 +13797,10 @@
         <v>112</v>
       </c>
       <c r="J85" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K85" t="s">
+        <v>820</v>
       </c>
       <c r="L85">
         <v>0.127</v>
@@ -13409,7 +13844,10 @@
         <v>112</v>
       </c>
       <c r="J86" t="s">
-        <v>376</v>
+        <v>841</v>
+      </c>
+      <c r="K86" t="s">
+        <v>842</v>
       </c>
       <c r="L86">
         <v>0.127</v>
@@ -13453,7 +13891,10 @@
         <v>112</v>
       </c>
       <c r="J87" t="s">
-        <v>376</v>
+        <v>841</v>
+      </c>
+      <c r="K87" t="s">
+        <v>842</v>
       </c>
       <c r="L87">
         <v>0.127</v>
@@ -13494,7 +13935,10 @@
         <v>112</v>
       </c>
       <c r="J88" t="s">
-        <v>376</v>
+        <v>843</v>
+      </c>
+      <c r="K88" t="s">
+        <v>844</v>
       </c>
       <c r="L88">
         <v>0.13800000000000001</v>
@@ -13535,7 +13979,10 @@
         <v>112</v>
       </c>
       <c r="J89" t="s">
-        <v>376</v>
+        <v>843</v>
+      </c>
+      <c r="K89" t="s">
+        <v>844</v>
       </c>
       <c r="L89">
         <v>9.1999999999999998E-2</v>
@@ -13576,7 +14023,10 @@
         <v>112</v>
       </c>
       <c r="J90" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K90" t="s">
+        <v>822</v>
       </c>
       <c r="L90">
         <v>0.75</v>
@@ -13617,7 +14067,10 @@
         <v>112</v>
       </c>
       <c r="J91" t="s">
-        <v>376</v>
+        <v>845</v>
+      </c>
+      <c r="K91" t="s">
+        <v>846</v>
       </c>
       <c r="L91">
         <v>0.7</v>
@@ -13658,7 +14111,10 @@
         <v>112</v>
       </c>
       <c r="J92" t="s">
-        <v>376</v>
+        <v>829</v>
+      </c>
+      <c r="K92" t="s">
+        <v>830</v>
       </c>
       <c r="L92">
         <v>0.441</v>
@@ -13699,7 +14155,10 @@
         <v>112</v>
       </c>
       <c r="J93" t="s">
-        <v>376</v>
+        <v>847</v>
+      </c>
+      <c r="K93" t="s">
+        <v>848</v>
       </c>
       <c r="L93">
         <v>0.22</v>
@@ -14142,7 +14601,10 @@
         <v>342</v>
       </c>
       <c r="J103" t="s">
-        <v>376</v>
+        <v>849</v>
+      </c>
+      <c r="K103" t="s">
+        <v>850</v>
       </c>
       <c r="L103">
         <v>0.6</v>
@@ -14186,7 +14648,10 @@
         <v>342</v>
       </c>
       <c r="J104" t="s">
-        <v>376</v>
+        <v>851</v>
+      </c>
+      <c r="K104" t="s">
+        <v>852</v>
       </c>
       <c r="L104">
         <v>1.65</v>
@@ -14227,7 +14692,10 @@
         <v>342</v>
       </c>
       <c r="J105" t="s">
-        <v>376</v>
+        <v>843</v>
+      </c>
+      <c r="K105" t="s">
+        <v>844</v>
       </c>
       <c r="L105">
         <v>3.05</v>
@@ -14271,7 +14739,10 @@
         <v>342</v>
       </c>
       <c r="J106" t="s">
-        <v>376</v>
+        <v>853</v>
+      </c>
+      <c r="K106" t="s">
+        <v>854</v>
       </c>
       <c r="L106">
         <v>0.36</v>
@@ -14312,7 +14783,10 @@
         <v>342</v>
       </c>
       <c r="J107" t="s">
-        <v>376</v>
+        <v>851</v>
+      </c>
+      <c r="K107" t="s">
+        <v>852</v>
       </c>
       <c r="L107">
         <v>0.182</v>
@@ -14353,7 +14827,10 @@
         <v>342</v>
       </c>
       <c r="J108" t="s">
-        <v>376</v>
+        <v>851</v>
+      </c>
+      <c r="K108" t="s">
+        <v>852</v>
       </c>
       <c r="L108">
         <v>0.109</v>
@@ -14394,7 +14871,10 @@
         <v>342</v>
       </c>
       <c r="J109" t="s">
-        <v>376</v>
+        <v>851</v>
+      </c>
+      <c r="K109" t="s">
+        <v>852</v>
       </c>
       <c r="L109">
         <v>0.13600000000000001</v>
@@ -14435,7 +14915,10 @@
         <v>342</v>
       </c>
       <c r="J110" t="s">
-        <v>376</v>
+        <v>851</v>
+      </c>
+      <c r="K110" t="s">
+        <v>852</v>
       </c>
       <c r="L110">
         <v>0.22</v>
@@ -14720,7 +15203,10 @@
         <v>375</v>
       </c>
       <c r="J116" t="s">
-        <v>376</v>
+        <v>855</v>
+      </c>
+      <c r="K116" t="s">
+        <v>856</v>
       </c>
       <c r="L116">
         <v>4.4999999999999998E-2</v>
@@ -14788,7 +15274,10 @@
         <v>375</v>
       </c>
       <c r="J117" t="s">
-        <v>376</v>
+        <v>855</v>
+      </c>
+      <c r="K117" t="s">
+        <v>856</v>
       </c>
       <c r="L117">
         <v>4.4999999999999998E-2</v>
@@ -14856,7 +15345,10 @@
         <v>375</v>
       </c>
       <c r="J118" t="s">
-        <v>376</v>
+        <v>855</v>
+      </c>
+      <c r="K118" t="s">
+        <v>856</v>
       </c>
       <c r="L118">
         <v>4.4999999999999998E-2</v>
@@ -14924,7 +15416,10 @@
         <v>375</v>
       </c>
       <c r="J119" t="s">
-        <v>376</v>
+        <v>857</v>
+      </c>
+      <c r="K119" t="s">
+        <v>858</v>
       </c>
       <c r="L119">
         <v>3.6999999999999998E-2</v>
@@ -14992,7 +15487,10 @@
         <v>375</v>
       </c>
       <c r="J120" t="s">
-        <v>376</v>
+        <v>857</v>
+      </c>
+      <c r="K120" t="s">
+        <v>858</v>
       </c>
       <c r="L120">
         <v>3.6999999999999998E-2</v>
@@ -15060,7 +15558,10 @@
         <v>375</v>
       </c>
       <c r="J121" t="s">
-        <v>376</v>
+        <v>857</v>
+      </c>
+      <c r="K121" t="s">
+        <v>858</v>
       </c>
       <c r="L121">
         <v>3.6999999999999998E-2</v>
@@ -15128,7 +15629,10 @@
         <v>375</v>
       </c>
       <c r="J122" t="s">
-        <v>376</v>
+        <v>851</v>
+      </c>
+      <c r="K122" t="s">
+        <v>852</v>
       </c>
       <c r="L122">
         <v>3.85E-2</v>
@@ -15225,7 +15729,10 @@
         <v>398</v>
       </c>
       <c r="J124" t="s">
-        <v>376</v>
+        <v>859</v>
+      </c>
+      <c r="K124" t="s">
+        <v>860</v>
       </c>
       <c r="L124">
         <v>0.45</v>
@@ -15293,7 +15800,10 @@
         <v>398</v>
       </c>
       <c r="J125" t="s">
-        <v>376</v>
+        <v>859</v>
+      </c>
+      <c r="K125" t="s">
+        <v>860</v>
       </c>
       <c r="L125">
         <v>0.45</v>
@@ -15361,7 +15871,10 @@
         <v>398</v>
       </c>
       <c r="J126" t="s">
-        <v>376</v>
+        <v>859</v>
+      </c>
+      <c r="K126" t="s">
+        <v>860</v>
       </c>
       <c r="L126">
         <v>0.45</v>
@@ -15429,7 +15942,10 @@
         <v>375</v>
       </c>
       <c r="J127" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K127" t="s">
+        <v>826</v>
       </c>
       <c r="L127">
         <v>0.65</v>
@@ -15497,7 +16013,10 @@
         <v>375</v>
       </c>
       <c r="J128" t="s">
-        <v>376</v>
+        <v>815</v>
+      </c>
+      <c r="K128" t="s">
+        <v>816</v>
       </c>
       <c r="L128">
         <v>0.56999999999999995</v>
@@ -15565,7 +16084,10 @@
         <v>375</v>
       </c>
       <c r="J129" t="s">
-        <v>376</v>
+        <v>839</v>
+      </c>
+      <c r="K129" t="s">
+        <v>840</v>
       </c>
       <c r="L129">
         <v>0.48</v>
@@ -15633,7 +16155,10 @@
         <v>375</v>
       </c>
       <c r="J130" t="s">
-        <v>376</v>
+        <v>857</v>
+      </c>
+      <c r="K130" t="s">
+        <v>858</v>
       </c>
       <c r="L130">
         <v>0.377</v>
@@ -15701,7 +16226,10 @@
         <v>375</v>
       </c>
       <c r="J131" t="s">
-        <v>376</v>
+        <v>857</v>
+      </c>
+      <c r="K131" t="s">
+        <v>858</v>
       </c>
       <c r="L131">
         <v>0.377</v>
@@ -15769,7 +16297,10 @@
         <v>375</v>
       </c>
       <c r="J132" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K132" t="s">
+        <v>826</v>
       </c>
       <c r="L132">
         <v>0.18</v>
@@ -15837,7 +16368,10 @@
         <v>375</v>
       </c>
       <c r="J133" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K133" t="s">
+        <v>826</v>
       </c>
       <c r="L133">
         <v>0.18</v>
@@ -15905,7 +16439,10 @@
         <v>375</v>
       </c>
       <c r="J134" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K134" t="s">
+        <v>826</v>
       </c>
       <c r="L134">
         <v>7.4999999999999997E-2</v>
@@ -15973,7 +16510,10 @@
         <v>375</v>
       </c>
       <c r="J135" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K135" t="s">
+        <v>826</v>
       </c>
       <c r="L135">
         <v>7.4999999999999997E-2</v>
@@ -16041,7 +16581,10 @@
         <v>375</v>
       </c>
       <c r="J136" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K136" t="s">
+        <v>826</v>
       </c>
       <c r="L136">
         <v>7.4999999999999997E-2</v>
@@ -16109,7 +16652,10 @@
         <v>375</v>
       </c>
       <c r="J137" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K137" t="s">
+        <v>826</v>
       </c>
       <c r="L137">
         <v>7.4999999999999997E-2</v>
@@ -16177,7 +16723,10 @@
         <v>375</v>
       </c>
       <c r="J138" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K138" t="s">
+        <v>826</v>
       </c>
       <c r="L138">
         <v>7.4999999999999997E-2</v>
@@ -16245,7 +16794,10 @@
         <v>375</v>
       </c>
       <c r="J139" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K139" t="s">
+        <v>826</v>
       </c>
       <c r="L139">
         <v>7.4999999999999997E-2</v>
@@ -16313,7 +16865,10 @@
         <v>375</v>
       </c>
       <c r="J140" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K140" t="s">
+        <v>826</v>
       </c>
       <c r="L140">
         <v>0.13800000000000001</v>
@@ -16381,7 +16936,10 @@
         <v>375</v>
       </c>
       <c r="J141" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K141" t="s">
+        <v>826</v>
       </c>
       <c r="L141">
         <v>0.13800000000000001</v>
@@ -16449,7 +17007,10 @@
         <v>375</v>
       </c>
       <c r="J142" t="s">
-        <v>376</v>
+        <v>861</v>
+      </c>
+      <c r="K142" t="s">
+        <v>862</v>
       </c>
       <c r="L142">
         <v>0.124</v>
@@ -16517,7 +17078,10 @@
         <v>375</v>
       </c>
       <c r="J143" t="s">
-        <v>376</v>
+        <v>861</v>
+      </c>
+      <c r="K143" t="s">
+        <v>862</v>
       </c>
       <c r="L143">
         <v>0.124</v>
@@ -16585,7 +17149,10 @@
         <v>375</v>
       </c>
       <c r="J144" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K144" t="s">
+        <v>826</v>
       </c>
       <c r="L144">
         <v>0.09</v>
@@ -16653,7 +17220,10 @@
         <v>375</v>
       </c>
       <c r="J145" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K145" t="s">
+        <v>826</v>
       </c>
       <c r="L145">
         <v>0.09</v>
@@ -16721,7 +17291,10 @@
         <v>375</v>
       </c>
       <c r="J146" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K146" t="s">
+        <v>820</v>
       </c>
       <c r="L146">
         <v>0.154</v>
@@ -16789,7 +17362,10 @@
         <v>375</v>
       </c>
       <c r="J147" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K147" t="s">
+        <v>820</v>
       </c>
       <c r="L147">
         <v>0.154</v>
@@ -16857,7 +17433,10 @@
         <v>375</v>
       </c>
       <c r="J148" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K148" t="s">
+        <v>820</v>
       </c>
       <c r="L148">
         <v>0.154</v>
@@ -16925,7 +17504,10 @@
         <v>375</v>
       </c>
       <c r="J149" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K149" t="s">
+        <v>838</v>
       </c>
       <c r="L149">
         <v>0.113</v>
@@ -16993,7 +17575,10 @@
         <v>375</v>
       </c>
       <c r="J150" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K150" t="s">
+        <v>838</v>
       </c>
       <c r="L150">
         <v>0.113</v>
@@ -17061,7 +17646,10 @@
         <v>375</v>
       </c>
       <c r="J151" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K151" t="s">
+        <v>838</v>
       </c>
       <c r="L151">
         <v>0.113</v>
@@ -17129,7 +17717,10 @@
         <v>375</v>
       </c>
       <c r="J152" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K152" t="s">
+        <v>838</v>
       </c>
       <c r="L152">
         <v>0.113</v>
@@ -17197,7 +17788,10 @@
         <v>375</v>
       </c>
       <c r="J153" t="s">
-        <v>376</v>
+        <v>837</v>
+      </c>
+      <c r="K153" t="s">
+        <v>838</v>
       </c>
       <c r="L153">
         <v>0.113</v>
@@ -17265,7 +17859,10 @@
         <v>398</v>
       </c>
       <c r="J154" t="s">
-        <v>376</v>
+        <v>839</v>
+      </c>
+      <c r="K154" t="s">
+        <v>840</v>
       </c>
       <c r="L154">
         <v>0.12690000000000001</v>
@@ -17333,7 +17930,10 @@
         <v>398</v>
       </c>
       <c r="J155" t="s">
-        <v>376</v>
+        <v>839</v>
+      </c>
+      <c r="K155" t="s">
+        <v>840</v>
       </c>
       <c r="L155">
         <v>0.12690000000000001</v>
@@ -17401,7 +18001,10 @@
         <v>398</v>
       </c>
       <c r="J156" t="s">
-        <v>376</v>
+        <v>839</v>
+      </c>
+      <c r="K156" t="s">
+        <v>840</v>
       </c>
       <c r="L156">
         <v>0.12690000000000001</v>
@@ -17469,7 +18072,10 @@
         <v>375</v>
       </c>
       <c r="J157" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K157" t="s">
+        <v>834</v>
       </c>
       <c r="L157">
         <v>0.126</v>
@@ -17537,7 +18143,10 @@
         <v>375</v>
       </c>
       <c r="J158" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K158" t="s">
+        <v>834</v>
       </c>
       <c r="L158">
         <v>0.126</v>
@@ -17605,7 +18214,10 @@
         <v>375</v>
       </c>
       <c r="J159" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K159" t="s">
+        <v>822</v>
       </c>
       <c r="L159">
         <v>0.14499999999999999</v>
@@ -17673,7 +18285,10 @@
         <v>375</v>
       </c>
       <c r="J160" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K160" t="s">
+        <v>822</v>
       </c>
       <c r="L160">
         <v>0.14499999999999999</v>
@@ -17741,7 +18356,10 @@
         <v>375</v>
       </c>
       <c r="J161" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K161" t="s">
+        <v>822</v>
       </c>
       <c r="L161">
         <v>0.14499999999999999</v>
@@ -17809,7 +18427,10 @@
         <v>375</v>
       </c>
       <c r="J162" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K162" t="s">
+        <v>822</v>
       </c>
       <c r="L162">
         <v>0.16900000000000001</v>
@@ -17877,7 +18498,10 @@
         <v>375</v>
       </c>
       <c r="J163" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K163" t="s">
+        <v>822</v>
       </c>
       <c r="L163">
         <v>0.16900000000000001</v>
@@ -17945,7 +18569,10 @@
         <v>375</v>
       </c>
       <c r="J164" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K164" t="s">
+        <v>822</v>
       </c>
       <c r="L164">
         <v>0.16900000000000001</v>
@@ -18013,7 +18640,10 @@
         <v>375</v>
       </c>
       <c r="J165" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K165" t="s">
+        <v>826</v>
       </c>
       <c r="L165">
         <v>6.3E-2</v>
@@ -18081,7 +18711,10 @@
         <v>375</v>
       </c>
       <c r="J166" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K166" t="s">
+        <v>826</v>
       </c>
       <c r="L166">
         <v>6.3E-2</v>
@@ -18149,7 +18782,10 @@
         <v>375</v>
       </c>
       <c r="J167" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K167" t="s">
+        <v>826</v>
       </c>
       <c r="L167">
         <v>6.3E-2</v>
@@ -18217,7 +18853,10 @@
         <v>375</v>
       </c>
       <c r="J168" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K168" t="s">
+        <v>820</v>
       </c>
       <c r="L168">
         <v>0.113</v>
@@ -18285,7 +18924,10 @@
         <v>375</v>
       </c>
       <c r="J169" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K169" t="s">
+        <v>820</v>
       </c>
       <c r="L169">
         <v>0.113</v>
@@ -18353,7 +18995,10 @@
         <v>375</v>
       </c>
       <c r="J170" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K170" t="s">
+        <v>820</v>
       </c>
       <c r="L170">
         <v>0.113</v>
@@ -18421,7 +19066,10 @@
         <v>375</v>
       </c>
       <c r="J171" t="s">
-        <v>376</v>
+        <v>819</v>
+      </c>
+      <c r="K171" t="s">
+        <v>820</v>
       </c>
       <c r="L171">
         <v>0.113</v>
@@ -18489,7 +19137,10 @@
         <v>375</v>
       </c>
       <c r="J172" t="s">
-        <v>376</v>
+        <v>839</v>
+      </c>
+      <c r="K172" t="s">
+        <v>840</v>
       </c>
       <c r="L172">
         <v>0.113</v>
@@ -18557,7 +19208,10 @@
         <v>375</v>
       </c>
       <c r="J173" t="s">
-        <v>376</v>
+        <v>839</v>
+      </c>
+      <c r="K173" t="s">
+        <v>840</v>
       </c>
       <c r="L173">
         <v>0.113</v>
@@ -18625,7 +19279,10 @@
         <v>375</v>
       </c>
       <c r="J174" t="s">
-        <v>376</v>
+        <v>841</v>
+      </c>
+      <c r="K174" t="s">
+        <v>842</v>
       </c>
       <c r="L174">
         <v>0.128</v>
@@ -18693,7 +19350,10 @@
         <v>375</v>
       </c>
       <c r="J175" t="s">
-        <v>376</v>
+        <v>841</v>
+      </c>
+      <c r="K175" t="s">
+        <v>842</v>
       </c>
       <c r="L175">
         <v>0.128</v>
@@ -18761,7 +19421,10 @@
         <v>375</v>
       </c>
       <c r="J176" t="s">
-        <v>376</v>
+        <v>841</v>
+      </c>
+      <c r="K176" t="s">
+        <v>842</v>
       </c>
       <c r="L176">
         <v>0.128</v>
@@ -18829,7 +19492,10 @@
         <v>375</v>
       </c>
       <c r="J177" t="s">
-        <v>376</v>
+        <v>841</v>
+      </c>
+      <c r="K177" t="s">
+        <v>842</v>
       </c>
       <c r="L177">
         <v>0.128</v>
@@ -18897,7 +19563,10 @@
         <v>375</v>
       </c>
       <c r="J178" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K178" t="s">
+        <v>828</v>
       </c>
       <c r="L178">
         <v>0.113</v>
@@ -18965,7 +19634,10 @@
         <v>375</v>
       </c>
       <c r="J179" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K179" t="s">
+        <v>828</v>
       </c>
       <c r="L179">
         <v>0.113</v>
@@ -19033,7 +19705,10 @@
         <v>375</v>
       </c>
       <c r="J180" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K180" t="s">
+        <v>828</v>
       </c>
       <c r="L180">
         <v>0.113</v>
@@ -19101,7 +19776,10 @@
         <v>375</v>
       </c>
       <c r="J181" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K181" t="s">
+        <v>828</v>
       </c>
       <c r="L181">
         <v>0.113</v>
@@ -19169,7 +19847,10 @@
         <v>375</v>
       </c>
       <c r="J182" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K182" t="s">
+        <v>834</v>
       </c>
       <c r="L182">
         <v>0.1</v>
@@ -19237,7 +19918,10 @@
         <v>375</v>
       </c>
       <c r="J183" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K183" t="s">
+        <v>834</v>
       </c>
       <c r="L183">
         <v>0.1</v>
@@ -19305,7 +19989,10 @@
         <v>375</v>
       </c>
       <c r="J184" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K184" t="s">
+        <v>834</v>
       </c>
       <c r="L184">
         <v>0.1</v>
@@ -19373,7 +20060,10 @@
         <v>375</v>
       </c>
       <c r="J185" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K185" t="s">
+        <v>834</v>
       </c>
       <c r="L185">
         <v>0.1</v>
@@ -19441,7 +20131,10 @@
         <v>375</v>
       </c>
       <c r="J186" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K186" t="s">
+        <v>834</v>
       </c>
       <c r="L186">
         <v>0.1</v>
@@ -19509,7 +20202,10 @@
         <v>375</v>
       </c>
       <c r="J187" t="s">
-        <v>376</v>
+        <v>833</v>
+      </c>
+      <c r="K187" t="s">
+        <v>834</v>
       </c>
       <c r="L187">
         <v>0.1</v>
@@ -19577,7 +20273,10 @@
         <v>375</v>
       </c>
       <c r="J188" t="s">
-        <v>376</v>
+        <v>863</v>
+      </c>
+      <c r="K188" t="s">
+        <v>864</v>
       </c>
       <c r="L188">
         <v>0.05</v>
@@ -19645,7 +20344,10 @@
         <v>375</v>
       </c>
       <c r="J189" t="s">
-        <v>376</v>
+        <v>865</v>
+      </c>
+      <c r="K189" t="s">
+        <v>866</v>
       </c>
       <c r="L189">
         <v>0.09</v>
@@ -19713,7 +20415,10 @@
         <v>375</v>
       </c>
       <c r="J190" t="s">
-        <v>376</v>
+        <v>865</v>
+      </c>
+      <c r="K190" t="s">
+        <v>866</v>
       </c>
       <c r="L190">
         <v>0.09</v>
@@ -19781,7 +20486,10 @@
         <v>375</v>
       </c>
       <c r="J191" t="s">
-        <v>376</v>
+        <v>861</v>
+      </c>
+      <c r="K191" t="s">
+        <v>862</v>
       </c>
       <c r="L191">
         <v>0.124</v>
@@ -19849,7 +20557,10 @@
         <v>375</v>
       </c>
       <c r="J192" t="s">
-        <v>376</v>
+        <v>861</v>
+      </c>
+      <c r="K192" t="s">
+        <v>862</v>
       </c>
       <c r="L192">
         <v>0.124</v>
@@ -19917,7 +20628,10 @@
         <v>375</v>
       </c>
       <c r="J193" t="s">
-        <v>376</v>
+        <v>823</v>
+      </c>
+      <c r="K193" t="s">
+        <v>824</v>
       </c>
       <c r="L193">
         <v>0.22</v>
@@ -19985,7 +20699,10 @@
         <v>375</v>
       </c>
       <c r="J194" t="s">
-        <v>376</v>
+        <v>823</v>
+      </c>
+      <c r="K194" t="s">
+        <v>824</v>
       </c>
       <c r="L194">
         <v>0.22</v>
@@ -20053,7 +20770,10 @@
         <v>375</v>
       </c>
       <c r="J195" t="s">
-        <v>376</v>
+        <v>823</v>
+      </c>
+      <c r="K195" t="s">
+        <v>824</v>
       </c>
       <c r="L195">
         <v>0.22</v>
@@ -20121,7 +20841,10 @@
         <v>375</v>
       </c>
       <c r="J196" t="s">
-        <v>376</v>
+        <v>823</v>
+      </c>
+      <c r="K196" t="s">
+        <v>824</v>
       </c>
       <c r="L196">
         <v>0.22</v>
@@ -20189,7 +20912,10 @@
         <v>375</v>
       </c>
       <c r="J197" t="s">
-        <v>376</v>
+        <v>823</v>
+      </c>
+      <c r="K197" t="s">
+        <v>824</v>
       </c>
       <c r="L197">
         <v>0.22</v>
@@ -20257,7 +20983,10 @@
         <v>375</v>
       </c>
       <c r="J198" t="s">
-        <v>376</v>
+        <v>823</v>
+      </c>
+      <c r="K198" t="s">
+        <v>824</v>
       </c>
       <c r="L198">
         <v>0.22</v>
@@ -20325,7 +21054,10 @@
         <v>375</v>
       </c>
       <c r="J199" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K199" t="s">
+        <v>828</v>
       </c>
       <c r="L199">
         <v>0.12</v>
@@ -20393,7 +21125,10 @@
         <v>375</v>
       </c>
       <c r="J200" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K200" t="s">
+        <v>828</v>
       </c>
       <c r="L200">
         <v>0.12</v>
@@ -20461,7 +21196,10 @@
         <v>375</v>
       </c>
       <c r="J201" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K201" t="s">
+        <v>828</v>
       </c>
       <c r="L201">
         <v>0.12</v>
@@ -20529,7 +21267,10 @@
         <v>375</v>
       </c>
       <c r="J202" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K202" t="s">
+        <v>828</v>
       </c>
       <c r="L202">
         <v>0.12</v>
@@ -20597,7 +21338,10 @@
         <v>398</v>
       </c>
       <c r="J203" t="s">
-        <v>376</v>
+        <v>861</v>
+      </c>
+      <c r="K203" t="s">
+        <v>862</v>
       </c>
       <c r="L203">
         <v>0.28599999999999998</v>
@@ -20662,7 +21406,10 @@
         <v>375</v>
       </c>
       <c r="J204" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K204" t="s">
+        <v>822</v>
       </c>
       <c r="L204">
         <v>5.5E-2</v>
@@ -20727,7 +21474,10 @@
         <v>375</v>
       </c>
       <c r="J205" t="s">
-        <v>376</v>
+        <v>821</v>
+      </c>
+      <c r="K205" t="s">
+        <v>822</v>
       </c>
       <c r="L205">
         <v>5.5E-2</v>
@@ -20795,7 +21545,10 @@
         <v>398</v>
       </c>
       <c r="J206" t="s">
-        <v>376</v>
+        <v>861</v>
+      </c>
+      <c r="K206" t="s">
+        <v>862</v>
       </c>
       <c r="L206">
         <v>0.28599999999999998</v>
@@ -20860,7 +21613,10 @@
         <v>375</v>
       </c>
       <c r="J207" t="s">
-        <v>376</v>
+        <v>867</v>
+      </c>
+      <c r="K207" t="s">
+        <v>868</v>
       </c>
       <c r="L207">
         <v>0.57799999999999996</v>
@@ -20901,7 +21657,10 @@
         <v>375</v>
       </c>
       <c r="J208" t="s">
-        <v>376</v>
+        <v>869</v>
+      </c>
+      <c r="K208" t="s">
+        <v>870</v>
       </c>
       <c r="L208">
         <v>0.76</v>
@@ -20942,7 +21701,10 @@
         <v>375</v>
       </c>
       <c r="J209" t="s">
-        <v>376</v>
+        <v>871</v>
+      </c>
+      <c r="K209" t="s">
+        <v>872</v>
       </c>
       <c r="L209">
         <v>0.6</v>
@@ -20983,7 +21745,10 @@
         <v>375</v>
       </c>
       <c r="J210" t="s">
-        <v>376</v>
+        <v>873</v>
+      </c>
+      <c r="K210" t="s">
+        <v>874</v>
       </c>
       <c r="L210">
         <v>0.7</v>
@@ -21024,7 +21789,10 @@
         <v>398</v>
       </c>
       <c r="J211" t="s">
-        <v>376</v>
+        <v>875</v>
+      </c>
+      <c r="K211" t="s">
+        <v>876</v>
       </c>
       <c r="L211">
         <v>0.182</v>
@@ -21065,7 +21833,10 @@
         <v>375</v>
       </c>
       <c r="J212" t="s">
-        <v>376</v>
+        <v>869</v>
+      </c>
+      <c r="K212" t="s">
+        <v>870</v>
       </c>
       <c r="L212">
         <v>0.1</v>
@@ -21109,7 +21880,10 @@
         <v>94</v>
       </c>
       <c r="J213" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K213" t="s">
+        <v>826</v>
       </c>
       <c r="L213">
         <v>0.09</v>
@@ -21153,7 +21927,10 @@
         <v>94</v>
       </c>
       <c r="J214" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K214" t="s">
+        <v>826</v>
       </c>
       <c r="L214">
         <v>0.09</v>
@@ -21197,7 +21974,10 @@
         <v>94</v>
       </c>
       <c r="J215" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K215" t="s">
+        <v>826</v>
       </c>
       <c r="L215">
         <v>0.09</v>
@@ -21241,7 +22021,10 @@
         <v>94</v>
       </c>
       <c r="J216" t="s">
-        <v>376</v>
+        <v>825</v>
+      </c>
+      <c r="K216" t="s">
+        <v>826</v>
       </c>
       <c r="L216">
         <v>0.09</v>
@@ -21285,7 +22068,10 @@
         <v>94</v>
       </c>
       <c r="J217" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K217" t="s">
+        <v>828</v>
       </c>
       <c r="L217">
         <v>7.4999999999999997E-2</v>
@@ -21329,7 +22115,10 @@
         <v>94</v>
       </c>
       <c r="J218" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K218" t="s">
+        <v>828</v>
       </c>
       <c r="L218">
         <v>7.4999999999999997E-2</v>
@@ -21373,7 +22162,10 @@
         <v>94</v>
       </c>
       <c r="J219" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K219" t="s">
+        <v>828</v>
       </c>
       <c r="L219">
         <v>7.4999999999999997E-2</v>
@@ -21417,7 +22209,10 @@
         <v>94</v>
       </c>
       <c r="J220" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K220" t="s">
+        <v>828</v>
       </c>
       <c r="L220">
         <v>7.4999999999999997E-2</v>
@@ -21461,7 +22256,10 @@
         <v>94</v>
       </c>
       <c r="J221" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K221" t="s">
+        <v>828</v>
       </c>
       <c r="L221">
         <v>0.12</v>
@@ -21505,7 +22303,10 @@
         <v>94</v>
       </c>
       <c r="J222" t="s">
-        <v>376</v>
+        <v>827</v>
+      </c>
+      <c r="K222" t="s">
+        <v>828</v>
       </c>
       <c r="L222">
         <v>0.12</v>

--- a/VerveStacks_NGA_grids_kan/source_data/VerveStacks_NGA.xlsx
+++ b/VerveStacks_NGA_grids_kan/source_data/VerveStacks_NGA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB90D96E-B45F-448E-99F8-4D9F38BB0D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ED84A03-421A-4AB4-9E24-4BB0D493B236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="32" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="31" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="30" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="29" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="28" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="37" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="36" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="35" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="34" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="33" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="9" r:id="rId6"/>
     <sheet name="historical_data" sheetId="8" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -2818,7 +2818,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B19D240-C7E8-D933-AF92-808DFE9FC623}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7235A42-8838-4FF3-5038-A3E387E4A044}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2873,7 +2873,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8B9C95A-9DA8-AAF8-448D-1CDDE98123D3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0450B95-F98D-B8F7-E504-B24EE5393D6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441581E1-4099-466A-AA80-7FF10D172D23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4800E43-117B-4996-A0B2-0E43DC5C89CA}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6352,7 +6352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9704369-0AAD-40A8-BAC5-26DA5C69AD12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A5755C-2BD4-486C-9395-B71D1AF87631}">
   <dimension ref="B2:L9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6612,7 +6612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D02AC9-95C8-4844-8A2D-A1067AACC1C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535DCE31-9F35-4526-8C58-05F85C8BCA0B}">
   <dimension ref="B2:J104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9585,7 +9585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77932D2E-1552-489F-AC40-C8E47E4BC1FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525C4F2E-140E-4C79-A703-2B4056DAA489}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10013,7 +10013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA064FA2-B2F3-4DD5-9D5F-677A200A70CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A727BF6-42D0-4D48-A85C-FAA592A80476}">
   <dimension ref="A1:Y233"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22356,7 +22356,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q223">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.45">
@@ -22391,7 +22391,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q224">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.45">
@@ -22426,7 +22426,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="Q225">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
     </row>
     <row r="226" spans="1:17" x14ac:dyDescent="0.45">

--- a/VerveStacks_NGA_grids_kan/source_data/VerveStacks_NGA.xlsx
+++ b/VerveStacks_NGA_grids_kan/source_data/VerveStacks_NGA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ED84A03-421A-4AB4-9E24-4BB0D493B236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44AB2493-1524-469A-A2C5-5EB186620750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="37" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="36" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="35" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="34" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="33" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="42" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="41" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="40" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="39" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="38" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="9" r:id="rId6"/>
     <sheet name="historical_data" sheetId="8" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -2818,7 +2818,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7235A42-8838-4FF3-5038-A3E387E4A044}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FACAB9DA-1DAF-92CE-E6D9-9D2AEEDCD3E7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2873,7 +2873,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0450B95-F98D-B8F7-E504-B24EE5393D6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29068C21-564B-70F1-719D-440354D747FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4800E43-117B-4996-A0B2-0E43DC5C89CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF58FB15-5A52-4C93-BFFD-3FD861036DB0}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6352,7 +6352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A5755C-2BD4-486C-9395-B71D1AF87631}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916A16C6-4881-4D21-BB0F-D38D1AA8B10E}">
   <dimension ref="B2:L9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6612,7 +6612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535DCE31-9F35-4526-8C58-05F85C8BCA0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCB43C4-4035-44D3-B762-9ECFDD9B578C}">
   <dimension ref="B2:J104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9585,7 +9585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525C4F2E-140E-4C79-A703-2B4056DAA489}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD04E5D1-C99C-4DA3-B540-8EF24B706FE7}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10013,7 +10013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A727BF6-42D0-4D48-A85C-FAA592A80476}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BE9515-7F06-4D54-A190-03150F7A2F17}">
   <dimension ref="A1:Y233"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
